--- a/excel/ExcelRA2/operacions_SV.xlsx
+++ b/excel/ExcelRA2/operacions_SV.xlsx
@@ -8,17 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/excel/ExcelRA2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{A32E9934-AA5A-4D5E-A431-DF3084F289FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF09E14A-3A42-4C92-9573-5894DB115F06}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="8_{A32E9934-AA5A-4D5E-A431-DF3084F289FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{827150F6-6176-4A4D-A92C-8412698F7CE9}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-8880" windowWidth="29070" windowHeight="15750" tabRatio="807" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" tabRatio="807" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lists" sheetId="1" r:id="rId1"/>
     <sheet name="sales_orders" sheetId="2" r:id="rId2"/>
-    <sheet name="sales_order_lines" sheetId="3" r:id="rId3"/>
-    <sheet name="plant_outputs" sheetId="7" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="8" r:id="rId3"/>
+    <sheet name="sales_order_lines" sheetId="3" r:id="rId4"/>
+    <sheet name="Hoja2" sheetId="9" r:id="rId5"/>
+    <sheet name="plant_outputs" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="5" r:id="rId8"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="580">
   <si>
     <t>currencies</t>
   </si>
@@ -1755,6 +1761,27 @@
   </si>
   <si>
     <t>DOL</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>(en blanco)</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Suma de qty</t>
+  </si>
+  <si>
+    <t>Cuenta de qty</t>
+  </si>
+  <si>
+    <t>(Todas)</t>
+  </si>
+  <si>
+    <t>importe</t>
   </si>
 </sst>
 </file>
@@ -1804,14 +1831,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1826,6 +1864,4396 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[operacions_SV.xlsx]Hoja1!TablaDinámica1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cuenta de qty</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>IT-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>IT-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IT-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(en blanco)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1D91-45BD-9712-E47626334489}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Suma de qty</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>IT-01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>IT-02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>IT-03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>(en blanco)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$4:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>17266</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9976</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10824</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1D91-45BD-9712-E47626334489}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="743018784"/>
+        <c:axId val="743017344"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="743018784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="743017344"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="743017344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="743018784"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[operacions_SV.xlsx]Hoja2!TablaDinámica1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Hoja2!$A$4:$A$14</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="7"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>IT-01</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>IT-02</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>IT-03</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>IT-01</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>IT-02</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>IT-03</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>(en blanco)</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>PL-01</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>PL-02</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>(en blanco)</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja2!$B$4:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>31288</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30255</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30277</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30094</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32512</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C46A-4BA0-A21E-45124B717BB7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1666400879"/>
+        <c:axId val="1666401839"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1666400879"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1666401839"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1666401839"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1666400879"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4BD6A5E-C67F-1333-684E-64358000FF95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA37B36-C979-C46A-84DC-3FEFA6406713}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Llorenç Huguet Boren" refreshedDate="45971.705067939816" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{77C36A17-49BD-4843-A1F5-355E19EE1D2F}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G1048576" sheet="sales_order_lines"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="so_id" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="line_no" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="item_id" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="IT-03"/>
+        <s v="IT-02"/>
+        <s v="IT-01"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="qty" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="127" maxValue="2000"/>
+    </cacheField>
+    <cacheField name="uom" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="unit_price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.2" maxValue="1.3"/>
+    </cacheField>
+    <cacheField name="currency" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="EUR"/>
+        <s v="DOL"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Llorenç Huguet Boren" refreshedDate="45972.585985532409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="181" xr:uid="{1D5DE1A3-79A9-4C3E-9282-ED1F45068F61}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F1048576" sheet="plant_outputs"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="id" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="output_date" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="plant_id" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="PL-01"/>
+        <s v="PL-02"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="item_id" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <s v="IT-01"/>
+        <s v="IT-02"/>
+        <s v="IT-03"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="qty" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="509" maxValue="1494"/>
+    </cacheField>
+    <cacheField name="uom" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="61">
+  <r>
+    <s v="SO-0001"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="2000"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0002"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="921"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0003"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="372"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0004"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="367"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0005"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="373"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0006"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="905"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0007"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="978"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0008"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="518"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0009"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="628"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0010"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="525"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0011"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="748"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0012"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="665"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0013"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="840"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0014"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="767"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0015"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="571"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0016"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="415"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0017"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="395"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0018"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="970"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0019"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="538"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0020"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="525"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0021"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="826"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0022"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="186"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0023"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="280"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0024"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="900"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0025"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="890"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0026"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="704"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0027"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="128"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0028"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="231"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0029"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="424"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0030"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="141"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0031"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="996"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0032"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="921"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0033"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="528"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0034"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="928"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0035"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="950"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0036"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="805"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0037"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="159"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0038"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="694"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0039"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="302"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0040"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="718"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0041"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="579"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0042"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="353"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0043"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="787"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0044"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="852"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0045"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="329"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0046"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="357"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0047"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="499"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0048"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="607"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0049"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="907"/>
+    <s v="KG"/>
+    <n v="1.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0050"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="967"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0051"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="465"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0052"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="398"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0053"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="592"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0054"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="867"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0055"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="127"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0056"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="923"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="SO-0057"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="583"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0058"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="888"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0059"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="800"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="SO-0060"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="454"/>
+    <s v="KG"/>
+    <n v="1.2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="181">
+  <r>
+    <s v="PO-0001"/>
+    <s v="2025-09-01"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1039"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0002"/>
+    <s v="2025-09-01"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="548"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0003"/>
+    <s v="2025-09-01"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1208"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0004"/>
+    <s v="2025-09-01"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="983"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0005"/>
+    <s v="2025-09-01"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1185"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0006"/>
+    <s v="2025-09-01"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="616"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0007"/>
+    <s v="2025-09-02"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1353"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0008"/>
+    <s v="2025-09-02"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1451"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0009"/>
+    <s v="2025-09-02"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="864"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0010"/>
+    <s v="2025-09-02"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="925"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0011"/>
+    <s v="2025-09-02"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="667"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0012"/>
+    <s v="2025-09-02"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="939"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0013"/>
+    <s v="2025-09-03"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="652"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0014"/>
+    <s v="2025-09-03"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="797"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0015"/>
+    <s v="2025-09-03"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1480"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0016"/>
+    <s v="2025-09-03"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="957"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0017"/>
+    <s v="2025-09-03"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1027"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0018"/>
+    <s v="2025-09-03"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1038"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0019"/>
+    <s v="2025-09-04"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="893"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0020"/>
+    <s v="2025-09-04"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1244"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0021"/>
+    <s v="2025-09-04"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1044"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0022"/>
+    <s v="2025-09-04"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1011"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0023"/>
+    <s v="2025-09-04"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1047"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0024"/>
+    <s v="2025-09-04"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1430"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0025"/>
+    <s v="2025-09-05"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1054"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0026"/>
+    <s v="2025-09-05"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="980"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0027"/>
+    <s v="2025-09-05"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1049"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0028"/>
+    <s v="2025-09-05"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="548"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0029"/>
+    <s v="2025-09-05"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1215"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0030"/>
+    <s v="2025-09-05"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="939"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0031"/>
+    <s v="2025-09-06"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1057"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0032"/>
+    <s v="2025-09-06"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1491"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0033"/>
+    <s v="2025-09-06"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1320"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0034"/>
+    <s v="2025-09-06"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1329"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0035"/>
+    <s v="2025-09-06"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="650"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0036"/>
+    <s v="2025-09-06"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1246"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0037"/>
+    <s v="2025-09-07"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1451"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0038"/>
+    <s v="2025-09-07"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1074"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0039"/>
+    <s v="2025-09-07"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="856"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0040"/>
+    <s v="2025-09-07"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="933"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0041"/>
+    <s v="2025-09-07"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1223"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0042"/>
+    <s v="2025-09-07"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1351"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0043"/>
+    <s v="2025-09-08"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="650"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0044"/>
+    <s v="2025-09-08"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1201"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0045"/>
+    <s v="2025-09-08"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="878"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0046"/>
+    <s v="2025-09-08"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1485"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0047"/>
+    <s v="2025-09-08"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1111"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0048"/>
+    <s v="2025-09-08"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="543"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0049"/>
+    <s v="2025-09-09"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1376"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0050"/>
+    <s v="2025-09-09"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1492"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0051"/>
+    <s v="2025-09-09"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1355"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0052"/>
+    <s v="2025-09-09"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="822"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0053"/>
+    <s v="2025-09-09"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="825"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0054"/>
+    <s v="2025-09-09"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1212"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0055"/>
+    <s v="2025-09-10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="518"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0056"/>
+    <s v="2025-09-10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="863"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0057"/>
+    <s v="2025-09-10"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="692"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0058"/>
+    <s v="2025-09-10"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="914"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0059"/>
+    <s v="2025-09-10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1104"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0060"/>
+    <s v="2025-09-10"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1315"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0061"/>
+    <s v="2025-09-11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1188"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0062"/>
+    <s v="2025-09-11"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="696"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0063"/>
+    <s v="2025-09-11"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="982"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0064"/>
+    <s v="2025-09-11"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1307"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0065"/>
+    <s v="2025-09-11"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="696"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0066"/>
+    <s v="2025-09-11"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="733"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0067"/>
+    <s v="2025-09-12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1487"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0068"/>
+    <s v="2025-09-12"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1199"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0069"/>
+    <s v="2025-09-12"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="880"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0070"/>
+    <s v="2025-09-12"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="850"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0071"/>
+    <s v="2025-09-12"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1113"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0072"/>
+    <s v="2025-09-12"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="801"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0073"/>
+    <s v="2025-09-13"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="531"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0074"/>
+    <s v="2025-09-13"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1125"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0075"/>
+    <s v="2025-09-13"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1131"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0076"/>
+    <s v="2025-09-13"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="549"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0077"/>
+    <s v="2025-09-13"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1104"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0078"/>
+    <s v="2025-09-13"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1298"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0079"/>
+    <s v="2025-09-14"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1391"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0080"/>
+    <s v="2025-09-14"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="633"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0081"/>
+    <s v="2025-09-14"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="529"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0082"/>
+    <s v="2025-09-14"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1092"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0083"/>
+    <s v="2025-09-14"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1136"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0084"/>
+    <s v="2025-09-14"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1022"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0085"/>
+    <s v="2025-09-15"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1422"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0086"/>
+    <s v="2025-09-15"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1084"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0087"/>
+    <s v="2025-09-15"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="714"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0088"/>
+    <s v="2025-09-15"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1064"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0089"/>
+    <s v="2025-09-15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="927"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0090"/>
+    <s v="2025-09-15"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="848"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0091"/>
+    <s v="2025-09-16"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1024"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0092"/>
+    <s v="2025-09-16"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="840"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0093"/>
+    <s v="2025-09-16"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1139"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0094"/>
+    <s v="2025-09-16"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="701"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0095"/>
+    <s v="2025-09-16"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="913"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0096"/>
+    <s v="2025-09-16"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1189"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0097"/>
+    <s v="2025-09-17"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1363"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0098"/>
+    <s v="2025-09-17"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="873"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0099"/>
+    <s v="2025-09-17"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="513"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0100"/>
+    <s v="2025-09-17"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="621"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0101"/>
+    <s v="2025-09-17"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1407"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0102"/>
+    <s v="2025-09-17"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1246"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0103"/>
+    <s v="2025-09-18"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1208"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0104"/>
+    <s v="2025-09-18"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="878"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0105"/>
+    <s v="2025-09-18"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1399"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0106"/>
+    <s v="2025-09-18"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1193"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0107"/>
+    <s v="2025-09-18"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="640"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0108"/>
+    <s v="2025-09-18"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="628"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0109"/>
+    <s v="2025-09-19"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="760"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0110"/>
+    <s v="2025-09-19"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1288"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0111"/>
+    <s v="2025-09-19"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1466"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0112"/>
+    <s v="2025-09-19"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1446"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0113"/>
+    <s v="2025-09-19"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="538"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0114"/>
+    <s v="2025-09-19"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1451"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0115"/>
+    <s v="2025-09-20"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="794"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0116"/>
+    <s v="2025-09-20"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1165"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0117"/>
+    <s v="2025-09-20"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1133"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0118"/>
+    <s v="2025-09-20"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1113"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0119"/>
+    <s v="2025-09-20"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1372"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0120"/>
+    <s v="2025-09-20"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="618"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0121"/>
+    <s v="2025-09-21"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1198"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0122"/>
+    <s v="2025-09-21"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1139"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0123"/>
+    <s v="2025-09-21"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1494"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0124"/>
+    <s v="2025-09-21"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="780"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0125"/>
+    <s v="2025-09-21"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1463"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0126"/>
+    <s v="2025-09-21"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="677"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0127"/>
+    <s v="2025-09-22"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1196"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0128"/>
+    <s v="2025-09-22"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1076"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0129"/>
+    <s v="2025-09-22"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="735"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0130"/>
+    <s v="2025-09-22"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1049"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0131"/>
+    <s v="2025-09-22"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="515"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0132"/>
+    <s v="2025-09-22"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1430"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0133"/>
+    <s v="2025-09-23"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="631"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0134"/>
+    <s v="2025-09-23"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="703"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0135"/>
+    <s v="2025-09-23"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="696"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0136"/>
+    <s v="2025-09-23"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="649"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0137"/>
+    <s v="2025-09-23"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1087"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0138"/>
+    <s v="2025-09-23"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1373"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0139"/>
+    <s v="2025-09-24"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1176"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0140"/>
+    <s v="2025-09-24"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="509"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0141"/>
+    <s v="2025-09-24"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="652"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0142"/>
+    <s v="2025-09-24"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1129"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0143"/>
+    <s v="2025-09-24"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1005"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0144"/>
+    <s v="2025-09-24"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1477"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0145"/>
+    <s v="2025-09-25"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="628"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0146"/>
+    <s v="2025-09-25"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1319"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0147"/>
+    <s v="2025-09-25"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1009"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0148"/>
+    <s v="2025-09-25"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1177"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0149"/>
+    <s v="2025-09-25"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="988"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0150"/>
+    <s v="2025-09-25"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="969"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0151"/>
+    <s v="2025-09-26"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1288"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0152"/>
+    <s v="2025-09-26"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1134"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0153"/>
+    <s v="2025-09-26"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1027"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0154"/>
+    <s v="2025-09-26"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1415"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0155"/>
+    <s v="2025-09-26"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="969"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0156"/>
+    <s v="2025-09-26"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1330"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0157"/>
+    <s v="2025-09-27"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1141"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0158"/>
+    <s v="2025-09-27"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="624"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0159"/>
+    <s v="2025-09-27"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1490"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0160"/>
+    <s v="2025-09-27"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="707"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0161"/>
+    <s v="2025-09-27"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1198"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0162"/>
+    <s v="2025-09-27"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1081"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0163"/>
+    <s v="2025-09-28"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="677"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0164"/>
+    <s v="2025-09-28"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="817"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0165"/>
+    <s v="2025-09-28"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="550"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0166"/>
+    <s v="2025-09-28"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1309"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0167"/>
+    <s v="2025-09-28"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="685"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0168"/>
+    <s v="2025-09-28"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1200"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0169"/>
+    <s v="2025-09-29"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1178"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0170"/>
+    <s v="2025-09-29"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1255"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0171"/>
+    <s v="2025-09-29"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1079"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0172"/>
+    <s v="2025-09-29"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="551"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0173"/>
+    <s v="2025-09-29"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="759"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0174"/>
+    <s v="2025-09-29"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1227"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0175"/>
+    <s v="2025-09-30"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="964"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0176"/>
+    <s v="2025-09-30"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="757"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0177"/>
+    <s v="2025-09-30"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="913"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0178"/>
+    <s v="2025-09-30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1485"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0179"/>
+    <s v="2025-09-30"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="531"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <s v="PO-0180"/>
+    <s v="2025-09-30"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1285"/>
+    <s v="KG"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <x v="3"/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8376931B-AA7E-4F06-9D71-D38A8838B705}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Cuenta de qty" fld="3" subtotal="count" baseField="2" baseItem="0"/>
+    <dataField name="Suma de qty" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5F7E753-F217-4F1A-9751-757E924312A9}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de qty" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1868,12 +6296,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tbl_sales_order_lines" displayName="Tbl_sales_order_lines" ref="A1:G61" totalsRowShown="0">
-  <autoFilter ref="A1:G61" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tbl_sales_order_lines" displayName="Tbl_sales_order_lines" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G61">
     <sortCondition ref="A1:A61"/>
   </sortState>
-  <tableColumns count="7">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="so_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="line_no"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="item_id"/>
@@ -1881,6 +6309,9 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="uom"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="unit_price"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="currency"/>
+    <tableColumn id="8" xr3:uid="{BC011E9E-6269-42AA-806F-F4CFA3992E6D}" name="importe" dataDxfId="0">
+      <calculatedColumnFormula>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1897,7 +6328,7 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="qty"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="uom"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="batch"/>
-    <tableColumn id="8" xr3:uid="{A61C7632-5A63-4F91-B6F5-721E439D5759}" name="Columna1" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{A61C7632-5A63-4F91-B6F5-721E439D5759}" name="Columna1" dataDxfId="1">
       <calculatedColumnFormula>DAY(Tbl_plant_outputs[[#This Row],[output_date]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2193,9 +6624,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2236,7 +6667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2276,8 +6707,12 @@
       <c r="M2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O2" t="str">
+        <f>VLOOKUP(Tbl_lists[[#This Row],[party_ids]],G2:I31,2)</f>
+        <v>DE</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2315,7 +6750,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2354,7 +6789,7 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -2386,7 +6821,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -2403,7 +6838,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>19</v>
       </c>
@@ -2417,7 +6852,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -2431,7 +6866,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G9" t="s">
         <v>126</v>
       </c>
@@ -2442,7 +6877,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G10" t="s">
         <v>539</v>
       </c>
@@ -2453,7 +6888,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G11" t="s">
         <v>123</v>
       </c>
@@ -2464,7 +6899,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G12" t="s">
         <v>116</v>
       </c>
@@ -2475,7 +6910,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G13" t="s">
         <v>113</v>
       </c>
@@ -2487,7 +6922,7 @@
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G14" t="s">
         <v>119</v>
       </c>
@@ -2498,7 +6933,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G15" t="s">
         <v>111</v>
       </c>
@@ -2509,7 +6944,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G16" t="s">
         <v>129</v>
       </c>
@@ -2520,7 +6955,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G17" t="s">
         <v>109</v>
       </c>
@@ -2531,7 +6966,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G18" t="s">
         <v>110</v>
       </c>
@@ -2542,7 +6977,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="19" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G19" t="s">
         <v>117</v>
       </c>
@@ -2553,7 +6988,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="20" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G20" t="s">
         <v>112</v>
       </c>
@@ -2564,7 +6999,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="21" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G21" t="s">
         <v>124</v>
       </c>
@@ -2575,7 +7010,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="22" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G22" t="s">
         <v>114</v>
       </c>
@@ -2586,7 +7021,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="23" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G23" t="s">
         <v>131</v>
       </c>
@@ -2597,7 +7032,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="24" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G24" t="s">
         <v>540</v>
       </c>
@@ -2608,7 +7043,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G25" t="s">
         <v>118</v>
       </c>
@@ -2619,7 +7054,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G26" t="s">
         <v>128</v>
       </c>
@@ -2630,7 +7065,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G27" t="s">
         <v>541</v>
       </c>
@@ -2641,7 +7076,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G28" t="s">
         <v>122</v>
       </c>
@@ -2652,7 +7087,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="29" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G29" t="s">
         <v>542</v>
       </c>
@@ -2663,7 +7098,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="30" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G30" t="s">
         <v>130</v>
       </c>
@@ -2674,7 +7109,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="31" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G31" t="s">
         <v>115</v>
       </c>
@@ -2697,9 +7132,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -2725,7 +7160,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -2751,7 +7186,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -2777,7 +7212,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -2803,7 +7238,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -2829,7 +7264,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -2855,7 +7290,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -2881,7 +7316,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -2907,7 +7342,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -2933,7 +7368,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -2959,7 +7394,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -2985,7 +7420,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -3011,7 +7446,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -3037,7 +7472,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -3063,7 +7498,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -3089,7 +7524,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -3115,7 +7550,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -3141,7 +7576,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>65</v>
       </c>
@@ -3167,7 +7602,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -3193,7 +7628,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -3219,7 +7654,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -3245,7 +7680,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -3271,7 +7706,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -3297,7 +7732,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -3323,7 +7758,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -3349,7 +7784,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -3375,7 +7810,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -3401,7 +7836,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>75</v>
       </c>
@@ -3427,7 +7862,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -3453,7 +7888,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -3479,7 +7914,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -3505,7 +7940,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -3531,7 +7966,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -3557,7 +7992,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -3583,7 +8018,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -3609,7 +8044,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -3635,7 +8070,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -3661,7 +8096,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -3687,7 +8122,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -3713,7 +8148,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -3739,7 +8174,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -3765,7 +8200,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -3791,7 +8226,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>90</v>
       </c>
@@ -3817,7 +8252,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -3843,7 +8278,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -3869,7 +8304,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -3895,7 +8330,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -3921,7 +8356,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -3947,7 +8382,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -3973,7 +8408,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -3999,7 +8434,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -4025,7 +8460,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>99</v>
       </c>
@@ -4051,7 +8486,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -4077,7 +8512,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>101</v>
       </c>
@@ -4103,7 +8538,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>102</v>
       </c>
@@ -4129,7 +8564,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>103</v>
       </c>
@@ -4155,7 +8590,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -4181,7 +8616,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>105</v>
       </c>
@@ -4207,7 +8642,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>106</v>
       </c>
@@ -4233,7 +8668,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>107</v>
       </c>
@@ -4259,7 +8694,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>108</v>
       </c>
@@ -4295,11 +8730,97 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB0BE0EF-C9FF-4125-BCA7-CA4157375D60}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4">
+        <v>17266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="4">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9976</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="4">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4">
+        <v>10824</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B8" s="4">
+        <v>60</v>
+      </c>
+      <c r="C8" s="4">
+        <v>38066</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4321,8 +8842,11 @@
       <c r="G1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -4333,7 +8857,7 @@
         <v>167</v>
       </c>
       <c r="D2">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
@@ -4344,8 +8868,12 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -4367,8 +8895,12 @@
       <c r="G3" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1197.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -4390,8 +8922,12 @@
       <c r="G4" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>483.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -4413,8 +8949,12 @@
       <c r="G5" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>477.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -4436,8 +8976,12 @@
       <c r="G6" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>484.90000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -4459,8 +9003,12 @@
       <c r="G7" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1176.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -4482,9 +9030,13 @@
       <c r="G8" t="s">
         <v>572</v>
       </c>
+      <c r="H8">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1271.4000000000001</v>
+      </c>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -4506,8 +9058,12 @@
       <c r="G9" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>673.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -4529,8 +9085,12 @@
       <c r="G10" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>816.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -4552,8 +9112,12 @@
       <c r="G11" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>682.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -4575,8 +9139,12 @@
       <c r="G12" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>972.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +9166,12 @@
       <c r="G13" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>864.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -4621,8 +9193,12 @@
       <c r="G14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -4644,8 +9220,12 @@
       <c r="G15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>920.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -4667,8 +9247,12 @@
       <c r="G16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>685.19999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -4690,8 +9274,12 @@
       <c r="G17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>65</v>
       </c>
@@ -4713,8 +9301,12 @@
       <c r="G18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -4736,8 +9328,12 @@
       <c r="G19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -4759,8 +9355,12 @@
       <c r="G20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>645.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -4782,8 +9382,12 @@
       <c r="G21" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -4805,8 +9409,12 @@
       <c r="G22" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>991.19999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -4828,8 +9436,12 @@
       <c r="G23" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>223.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -4851,8 +9463,12 @@
       <c r="G24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -4874,8 +9490,12 @@
       <c r="G25" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -4897,8 +9517,12 @@
       <c r="G26" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -4920,8 +9544,12 @@
       <c r="G27" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>844.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>75</v>
       </c>
@@ -4943,8 +9571,12 @@
       <c r="G28" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>153.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -4966,8 +9598,12 @@
       <c r="G29" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>300.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -4989,8 +9625,12 @@
       <c r="G30" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>551.20000000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -5012,8 +9652,12 @@
       <c r="G31" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>183.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -5035,8 +9679,12 @@
       <c r="G32" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1195.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -5058,8 +9706,12 @@
       <c r="G33" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1105.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -5081,8 +9733,12 @@
       <c r="G34" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>633.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -5104,8 +9760,12 @@
       <c r="G35" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1113.5999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -5127,8 +9787,12 @@
       <c r="G36" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -5150,8 +9814,12 @@
       <c r="G37" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>966</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -5173,8 +9841,12 @@
       <c r="G38" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>190.79999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -5196,8 +9868,12 @@
       <c r="G39" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>832.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -5219,8 +9895,12 @@
       <c r="G40" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>362.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -5242,8 +9922,12 @@
       <c r="G41" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>861.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -5265,8 +9949,12 @@
       <c r="G42" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>694.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>90</v>
       </c>
@@ -5288,8 +9976,12 @@
       <c r="G43" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>423.59999999999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -5311,8 +10003,12 @@
       <c r="G44" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>944.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -5334,8 +10030,12 @@
       <c r="G45" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1022.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -5357,8 +10057,12 @@
       <c r="G46" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>394.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -5380,8 +10084,12 @@
       <c r="G47" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>428.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -5403,8 +10111,12 @@
       <c r="G48" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>648.70000000000005</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -5426,8 +10138,12 @@
       <c r="G49" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>789.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -5449,8 +10165,12 @@
       <c r="G50" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1179.1000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -5472,8 +10192,12 @@
       <c r="G51" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1160.3999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>99</v>
       </c>
@@ -5495,8 +10219,12 @@
       <c r="G52" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -5518,8 +10246,12 @@
       <c r="G53" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>477.59999999999997</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>101</v>
       </c>
@@ -5541,8 +10273,12 @@
       <c r="G54" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>710.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>102</v>
       </c>
@@ -5564,8 +10300,12 @@
       <c r="G55" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1040.3999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>103</v>
       </c>
@@ -5587,8 +10327,12 @@
       <c r="G56" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>152.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -5610,8 +10354,12 @@
       <c r="G57" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1107.5999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>105</v>
       </c>
@@ -5633,8 +10381,12 @@
       <c r="G58" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>699.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>106</v>
       </c>
@@ -5656,8 +10408,12 @@
       <c r="G59" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>1065.5999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>107</v>
       </c>
@@ -5679,8 +10435,12 @@
       <c r="G60" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>108</v>
       </c>
@@ -5701,6 +10461,10 @@
       </c>
       <c r="G61" t="s">
         <v>11</v>
+      </c>
+      <c r="H61">
+        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
+        <v>544.79999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -5711,12 +10475,119 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EFB1EFC-9E09-49FA-9385-B0CEA0292B41}">
+  <dimension ref="A3:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4">
+        <v>91820</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4">
+        <v>31288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="4">
+        <v>30255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="4">
+        <v>30277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B8" s="4">
+        <v>91706</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="4">
+        <v>30094</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="4">
+        <v>29100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="4">
+        <v>32512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B14" s="4">
+        <v>183526</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -5742,7 +10613,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -5769,7 +10640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>178</v>
       </c>
@@ -5796,7 +10667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>179</v>
       </c>
@@ -5823,7 +10694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>180</v>
       </c>
@@ -5850,7 +10721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>181</v>
       </c>
@@ -5877,7 +10748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>182</v>
       </c>
@@ -5904,7 +10775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>183</v>
       </c>
@@ -5931,7 +10802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>184</v>
       </c>
@@ -5958,7 +10829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>185</v>
       </c>
@@ -5985,7 +10856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -6012,7 +10883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -6039,7 +10910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>188</v>
       </c>
@@ -6066,7 +10937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>189</v>
       </c>
@@ -6093,7 +10964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>190</v>
       </c>
@@ -6120,7 +10991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>191</v>
       </c>
@@ -6147,7 +11018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>192</v>
       </c>
@@ -6174,7 +11045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>193</v>
       </c>
@@ -6201,7 +11072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>194</v>
       </c>
@@ -6228,7 +11099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>195</v>
       </c>
@@ -6255,7 +11126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -6282,7 +11153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>197</v>
       </c>
@@ -6309,7 +11180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>198</v>
       </c>
@@ -6336,7 +11207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>199</v>
       </c>
@@ -6363,7 +11234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>200</v>
       </c>
@@ -6390,7 +11261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>201</v>
       </c>
@@ -6417,7 +11288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>202</v>
       </c>
@@ -6444,7 +11315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>203</v>
       </c>
@@ -6471,7 +11342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>204</v>
       </c>
@@ -6498,7 +11369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>205</v>
       </c>
@@ -6525,7 +11396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>206</v>
       </c>
@@ -6552,7 +11423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>207</v>
       </c>
@@ -6579,7 +11450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>208</v>
       </c>
@@ -6606,7 +11477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>209</v>
       </c>
@@ -6633,7 +11504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>210</v>
       </c>
@@ -6660,7 +11531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>211</v>
       </c>
@@ -6687,7 +11558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>212</v>
       </c>
@@ -6714,7 +11585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>213</v>
       </c>
@@ -6741,7 +11612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>214</v>
       </c>
@@ -6768,7 +11639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>215</v>
       </c>
@@ -6795,7 +11666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>216</v>
       </c>
@@ -6822,7 +11693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>217</v>
       </c>
@@ -6849,7 +11720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>218</v>
       </c>
@@ -6876,7 +11747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>219</v>
       </c>
@@ -6903,7 +11774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>220</v>
       </c>
@@ -6930,7 +11801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>221</v>
       </c>
@@ -6957,7 +11828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>222</v>
       </c>
@@ -6984,7 +11855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>223</v>
       </c>
@@ -7011,7 +11882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>224</v>
       </c>
@@ -7038,7 +11909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>225</v>
       </c>
@@ -7065,7 +11936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>226</v>
       </c>
@@ -7092,7 +11963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>227</v>
       </c>
@@ -7119,7 +11990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>228</v>
       </c>
@@ -7146,7 +12017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>229</v>
       </c>
@@ -7173,7 +12044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>230</v>
       </c>
@@ -7200,7 +12071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>231</v>
       </c>
@@ -7227,7 +12098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>232</v>
       </c>
@@ -7254,7 +12125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>233</v>
       </c>
@@ -7281,7 +12152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>234</v>
       </c>
@@ -7308,7 +12179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>235</v>
       </c>
@@ -7335,7 +12206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>236</v>
       </c>
@@ -7362,7 +12233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>237</v>
       </c>
@@ -7389,7 +12260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>238</v>
       </c>
@@ -7416,7 +12287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>239</v>
       </c>
@@ -7443,7 +12314,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>240</v>
       </c>
@@ -7470,7 +12341,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>241</v>
       </c>
@@ -7497,7 +12368,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>242</v>
       </c>
@@ -7524,7 +12395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>243</v>
       </c>
@@ -7551,7 +12422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>244</v>
       </c>
@@ -7578,7 +12449,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>245</v>
       </c>
@@ -7605,7 +12476,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>246</v>
       </c>
@@ -7632,7 +12503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>247</v>
       </c>
@@ -7659,7 +12530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>248</v>
       </c>
@@ -7686,7 +12557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>249</v>
       </c>
@@ -7713,7 +12584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>250</v>
       </c>
@@ -7740,7 +12611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>251</v>
       </c>
@@ -7767,7 +12638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>252</v>
       </c>
@@ -7794,7 +12665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>253</v>
       </c>
@@ -7821,7 +12692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>254</v>
       </c>
@@ -7848,7 +12719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>255</v>
       </c>
@@ -7875,7 +12746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>256</v>
       </c>
@@ -7902,7 +12773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>257</v>
       </c>
@@ -7929,7 +12800,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>258</v>
       </c>
@@ -7956,7 +12827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>259</v>
       </c>
@@ -7983,7 +12854,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>260</v>
       </c>
@@ -8010,7 +12881,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>261</v>
       </c>
@@ -8037,7 +12908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>262</v>
       </c>
@@ -8064,7 +12935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>263</v>
       </c>
@@ -8091,7 +12962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>264</v>
       </c>
@@ -8118,7 +12989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>265</v>
       </c>
@@ -8145,7 +13016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>266</v>
       </c>
@@ -8172,7 +13043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>267</v>
       </c>
@@ -8199,7 +13070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>268</v>
       </c>
@@ -8226,7 +13097,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>269</v>
       </c>
@@ -8253,7 +13124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>270</v>
       </c>
@@ -8280,7 +13151,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>271</v>
       </c>
@@ -8307,7 +13178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>272</v>
       </c>
@@ -8334,7 +13205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>273</v>
       </c>
@@ -8361,7 +13232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>274</v>
       </c>
@@ -8388,7 +13259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>275</v>
       </c>
@@ -8415,7 +13286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>276</v>
       </c>
@@ -8442,7 +13313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>277</v>
       </c>
@@ -8469,7 +13340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>278</v>
       </c>
@@ -8496,7 +13367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>279</v>
       </c>
@@ -8523,7 +13394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>280</v>
       </c>
@@ -8550,7 +13421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>281</v>
       </c>
@@ -8577,7 +13448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>282</v>
       </c>
@@ -8604,7 +13475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>283</v>
       </c>
@@ -8631,7 +13502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>284</v>
       </c>
@@ -8658,7 +13529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>285</v>
       </c>
@@ -8685,7 +13556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>286</v>
       </c>
@@ -8712,7 +13583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>287</v>
       </c>
@@ -8739,7 +13610,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>288</v>
       </c>
@@ -8766,7 +13637,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>289</v>
       </c>
@@ -8793,7 +13664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>290</v>
       </c>
@@ -8820,7 +13691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>291</v>
       </c>
@@ -8847,7 +13718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>292</v>
       </c>
@@ -8874,7 +13745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>293</v>
       </c>
@@ -8901,7 +13772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>294</v>
       </c>
@@ -8928,7 +13799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>295</v>
       </c>
@@ -8955,7 +13826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>296</v>
       </c>
@@ -8982,7 +13853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>297</v>
       </c>
@@ -9009,7 +13880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>298</v>
       </c>
@@ -9036,7 +13907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>299</v>
       </c>
@@ -9063,7 +13934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>300</v>
       </c>
@@ -9090,7 +13961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>301</v>
       </c>
@@ -9117,7 +13988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>302</v>
       </c>
@@ -9144,7 +14015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>303</v>
       </c>
@@ -9171,7 +14042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>304</v>
       </c>
@@ -9198,7 +14069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>305</v>
       </c>
@@ -9225,7 +14096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>306</v>
       </c>
@@ -9252,7 +14123,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>307</v>
       </c>
@@ -9279,7 +14150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>308</v>
       </c>
@@ -9306,7 +14177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>309</v>
       </c>
@@ -9333,7 +14204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>310</v>
       </c>
@@ -9360,7 +14231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>311</v>
       </c>
@@ -9387,7 +14258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>312</v>
       </c>
@@ -9414,7 +14285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>313</v>
       </c>
@@ -9441,7 +14312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>314</v>
       </c>
@@ -9468,7 +14339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>315</v>
       </c>
@@ -9495,7 +14366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>316</v>
       </c>
@@ -9522,7 +14393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>317</v>
       </c>
@@ -9549,7 +14420,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>318</v>
       </c>
@@ -9576,7 +14447,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>319</v>
       </c>
@@ -9603,7 +14474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>320</v>
       </c>
@@ -9630,7 +14501,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>321</v>
       </c>
@@ -9657,7 +14528,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>322</v>
       </c>
@@ -9684,7 +14555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>323</v>
       </c>
@@ -9711,7 +14582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>324</v>
       </c>
@@ -9738,7 +14609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>325</v>
       </c>
@@ -9765,7 +14636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>326</v>
       </c>
@@ -9792,7 +14663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>327</v>
       </c>
@@ -9819,7 +14690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>328</v>
       </c>
@@ -9846,7 +14717,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>329</v>
       </c>
@@ -9873,7 +14744,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>330</v>
       </c>
@@ -9900,7 +14771,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>331</v>
       </c>
@@ -9927,7 +14798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>332</v>
       </c>
@@ -9954,7 +14825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>333</v>
       </c>
@@ -9981,7 +14852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>334</v>
       </c>
@@ -10008,7 +14879,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>335</v>
       </c>
@@ -10035,7 +14906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>336</v>
       </c>
@@ -10062,7 +14933,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>337</v>
       </c>
@@ -10089,7 +14960,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>338</v>
       </c>
@@ -10116,7 +14987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>339</v>
       </c>
@@ -10143,7 +15014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>340</v>
       </c>
@@ -10170,7 +15041,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>341</v>
       </c>
@@ -10197,7 +15068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>342</v>
       </c>
@@ -10224,7 +15095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>343</v>
       </c>
@@ -10251,7 +15122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>344</v>
       </c>
@@ -10278,7 +15149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>345</v>
       </c>
@@ -10305,7 +15176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>346</v>
       </c>
@@ -10332,7 +15203,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>347</v>
       </c>
@@ -10359,7 +15230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>348</v>
       </c>
@@ -10386,7 +15257,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>349</v>
       </c>
@@ -10413,7 +15284,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>350</v>
       </c>
@@ -10440,7 +15311,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>351</v>
       </c>
@@ -10467,7 +15338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>352</v>
       </c>
@@ -10494,7 +15365,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>353</v>
       </c>
@@ -10521,7 +15392,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>354</v>
       </c>
@@ -10548,7 +15419,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>355</v>
       </c>
@@ -10575,7 +15446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>356</v>
       </c>

--- a/excel/ExcelRA2/operacions_SV.xlsx
+++ b/excel/ExcelRA2/operacions_SV.xlsx
@@ -8,23 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/excel/ExcelRA2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{A32E9934-AA5A-4D5E-A431-DF3084F289FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{827150F6-6176-4A4D-A92C-8412698F7CE9}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="8_{A32E9934-AA5A-4D5E-A431-DF3084F289FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3953A1-C75E-4BF8-B39E-54819C4CE8A8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" tabRatio="807" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lists" sheetId="1" r:id="rId1"/>
     <sheet name="sales_orders" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="8" r:id="rId3"/>
-    <sheet name="sales_order_lines" sheetId="3" r:id="rId4"/>
-    <sheet name="Hoja2" sheetId="9" r:id="rId5"/>
-    <sheet name="plant_outputs" sheetId="7" r:id="rId6"/>
+    <sheet name="sales_order_lines" sheetId="3" r:id="rId3"/>
+    <sheet name="plant_outputs" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
-    <pivotCache cacheId="5" r:id="rId8"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="573">
   <si>
     <t>currencies</t>
   </si>
@@ -1761,27 +1755,6 @@
   </si>
   <si>
     <t>DOL</t>
-  </si>
-  <si>
-    <t>Etiquetas de fila</t>
-  </si>
-  <si>
-    <t>(en blanco)</t>
-  </si>
-  <si>
-    <t>Total general</t>
-  </si>
-  <si>
-    <t>Suma de qty</t>
-  </si>
-  <si>
-    <t>Cuenta de qty</t>
-  </si>
-  <si>
-    <t>(Todas)</t>
-  </si>
-  <si>
-    <t>importe</t>
   </si>
 </sst>
 </file>
@@ -1831,25 +1804,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1864,4396 +1826,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[operacions_SV.xlsx]Hoja1!TablaDinámica1</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-ES"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-ES"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Hoja1!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Cuenta de qty</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Hoja1!$A$4:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>IT-01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>IT-02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>IT-03</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>(en blanco)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Hoja1!$B$4:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1D91-45BD-9712-E47626334489}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Hoja1!$C$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Suma de qty</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Hoja1!$A$4:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>IT-01</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>IT-02</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>IT-03</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>(en blanco)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Hoja1!$C$4:$C$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>17266</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9976</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10824</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1D91-45BD-9712-E47626334489}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="743018784"/>
-        <c:axId val="743017344"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="743018784"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="743017344"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="743017344"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="743018784"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[operacions_SV.xlsx]Hoja2!TablaDinámica1</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-ES"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Hoja2!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Hoja2!$A$4:$A$14</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="7"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>IT-01</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>IT-02</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>IT-03</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>IT-01</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>IT-02</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>IT-03</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>(en blanco)</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>PL-01</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>PL-02</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>(en blanco)</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Hoja2!$B$4:$B$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>31288</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>30255</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30277</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30094</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>29100</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>32512</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C46A-4BA0-A21E-45124B717BB7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1666400879"/>
-        <c:axId val="1666401839"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1666400879"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1666401839"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1666401839"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-ES"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1666400879"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-ES"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1095375</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4BD6A5E-C67F-1333-684E-64358000FF95}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA37B36-C979-C46A-84DC-3FEFA6406713}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Llorenç Huguet Boren" refreshedDate="45971.705067939816" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{77C36A17-49BD-4843-A1F5-355E19EE1D2F}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G1048576" sheet="sales_order_lines"/>
-  </cacheSource>
-  <cacheFields count="7">
-    <cacheField name="so_id" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="line_no" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
-    </cacheField>
-    <cacheField name="item_id" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
-        <s v="IT-03"/>
-        <s v="IT-02"/>
-        <s v="IT-01"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="qty" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="127" maxValue="2000"/>
-    </cacheField>
-    <cacheField name="uom" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="unit_price" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1.2" maxValue="1.3"/>
-    </cacheField>
-    <cacheField name="currency" numFmtId="0">
-      <sharedItems containsBlank="1" count="3">
-        <s v="EUR"/>
-        <s v="DOL"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Llorenç Huguet Boren" refreshedDate="45972.585985532409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="181" xr:uid="{1D5DE1A3-79A9-4C3E-9282-ED1F45068F61}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F1048576" sheet="plant_outputs"/>
-  </cacheSource>
-  <cacheFields count="6">
-    <cacheField name="id" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="output_date" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="plant_id" numFmtId="0">
-      <sharedItems containsBlank="1" count="3">
-        <s v="PL-01"/>
-        <s v="PL-02"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="item_id" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
-        <s v="IT-01"/>
-        <s v="IT-02"/>
-        <s v="IT-03"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="qty" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="509" maxValue="1494"/>
-    </cacheField>
-    <cacheField name="uom" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="61">
-  <r>
-    <s v="SO-0001"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="2000"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0002"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="921"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0003"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="372"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0004"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="367"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0005"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="373"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0006"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="905"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0007"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="978"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0008"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="518"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0009"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="628"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0010"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="525"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0011"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="748"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0012"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="665"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0013"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="840"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0014"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="767"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0015"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="571"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0016"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="415"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0017"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="395"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0018"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="970"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0019"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="538"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0020"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="525"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0021"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="826"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0022"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="186"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0023"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="280"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0024"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="900"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0025"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="890"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0026"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="704"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0027"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="128"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0028"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="231"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0029"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="424"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0030"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="141"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0031"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="996"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0032"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="921"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0033"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="528"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0034"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="928"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0035"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="950"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0036"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="805"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0037"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="159"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0038"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="694"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0039"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="302"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0040"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="718"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0041"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="579"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0042"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="353"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0043"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="787"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0044"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="852"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0045"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="329"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0046"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="357"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0047"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="499"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0048"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="607"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0049"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="907"/>
-    <s v="KG"/>
-    <n v="1.3"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0050"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="967"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0051"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="465"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0052"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="398"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0053"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="592"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0054"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="867"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0055"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="127"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0056"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="923"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <s v="SO-0057"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="583"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0058"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="888"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0059"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="800"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <s v="SO-0060"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="454"/>
-    <s v="KG"/>
-    <n v="1.2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <x v="3"/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="181">
-  <r>
-    <s v="PO-0001"/>
-    <s v="2025-09-01"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1039"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0002"/>
-    <s v="2025-09-01"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="548"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0003"/>
-    <s v="2025-09-01"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1208"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0004"/>
-    <s v="2025-09-01"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="983"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0005"/>
-    <s v="2025-09-01"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1185"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0006"/>
-    <s v="2025-09-01"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="616"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0007"/>
-    <s v="2025-09-02"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1353"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0008"/>
-    <s v="2025-09-02"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1451"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0009"/>
-    <s v="2025-09-02"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="864"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0010"/>
-    <s v="2025-09-02"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="925"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0011"/>
-    <s v="2025-09-02"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="667"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0012"/>
-    <s v="2025-09-02"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="939"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0013"/>
-    <s v="2025-09-03"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="652"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0014"/>
-    <s v="2025-09-03"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="797"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0015"/>
-    <s v="2025-09-03"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1480"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0016"/>
-    <s v="2025-09-03"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="957"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0017"/>
-    <s v="2025-09-03"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1027"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0018"/>
-    <s v="2025-09-03"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1038"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0019"/>
-    <s v="2025-09-04"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="893"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0020"/>
-    <s v="2025-09-04"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1244"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0021"/>
-    <s v="2025-09-04"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1044"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0022"/>
-    <s v="2025-09-04"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1011"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0023"/>
-    <s v="2025-09-04"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1047"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0024"/>
-    <s v="2025-09-04"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1430"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0025"/>
-    <s v="2025-09-05"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1054"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0026"/>
-    <s v="2025-09-05"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="980"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0027"/>
-    <s v="2025-09-05"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1049"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0028"/>
-    <s v="2025-09-05"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="548"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0029"/>
-    <s v="2025-09-05"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1215"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0030"/>
-    <s v="2025-09-05"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="939"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0031"/>
-    <s v="2025-09-06"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1057"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0032"/>
-    <s v="2025-09-06"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1491"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0033"/>
-    <s v="2025-09-06"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1320"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0034"/>
-    <s v="2025-09-06"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1329"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0035"/>
-    <s v="2025-09-06"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="650"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0036"/>
-    <s v="2025-09-06"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1246"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0037"/>
-    <s v="2025-09-07"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1451"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0038"/>
-    <s v="2025-09-07"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1074"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0039"/>
-    <s v="2025-09-07"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="856"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0040"/>
-    <s v="2025-09-07"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="933"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0041"/>
-    <s v="2025-09-07"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1223"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0042"/>
-    <s v="2025-09-07"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1351"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0043"/>
-    <s v="2025-09-08"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="650"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0044"/>
-    <s v="2025-09-08"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1201"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0045"/>
-    <s v="2025-09-08"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="878"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0046"/>
-    <s v="2025-09-08"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1485"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0047"/>
-    <s v="2025-09-08"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1111"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0048"/>
-    <s v="2025-09-08"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="543"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0049"/>
-    <s v="2025-09-09"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1376"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0050"/>
-    <s v="2025-09-09"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1492"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0051"/>
-    <s v="2025-09-09"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1355"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0052"/>
-    <s v="2025-09-09"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="822"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0053"/>
-    <s v="2025-09-09"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="825"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0054"/>
-    <s v="2025-09-09"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1212"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0055"/>
-    <s v="2025-09-10"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="518"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0056"/>
-    <s v="2025-09-10"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="863"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0057"/>
-    <s v="2025-09-10"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="692"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0058"/>
-    <s v="2025-09-10"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="914"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0059"/>
-    <s v="2025-09-10"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1104"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0060"/>
-    <s v="2025-09-10"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1315"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0061"/>
-    <s v="2025-09-11"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1188"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0062"/>
-    <s v="2025-09-11"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="696"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0063"/>
-    <s v="2025-09-11"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="982"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0064"/>
-    <s v="2025-09-11"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1307"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0065"/>
-    <s v="2025-09-11"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="696"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0066"/>
-    <s v="2025-09-11"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="733"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0067"/>
-    <s v="2025-09-12"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1487"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0068"/>
-    <s v="2025-09-12"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1199"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0069"/>
-    <s v="2025-09-12"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="880"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0070"/>
-    <s v="2025-09-12"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="850"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0071"/>
-    <s v="2025-09-12"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1113"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0072"/>
-    <s v="2025-09-12"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="801"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0073"/>
-    <s v="2025-09-13"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="531"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0074"/>
-    <s v="2025-09-13"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1125"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0075"/>
-    <s v="2025-09-13"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1131"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0076"/>
-    <s v="2025-09-13"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="549"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0077"/>
-    <s v="2025-09-13"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1104"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0078"/>
-    <s v="2025-09-13"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1298"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0079"/>
-    <s v="2025-09-14"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1391"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0080"/>
-    <s v="2025-09-14"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="633"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0081"/>
-    <s v="2025-09-14"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="529"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0082"/>
-    <s v="2025-09-14"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1092"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0083"/>
-    <s v="2025-09-14"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1136"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0084"/>
-    <s v="2025-09-14"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1022"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0085"/>
-    <s v="2025-09-15"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1422"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0086"/>
-    <s v="2025-09-15"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1084"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0087"/>
-    <s v="2025-09-15"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="714"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0088"/>
-    <s v="2025-09-15"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1064"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0089"/>
-    <s v="2025-09-15"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="927"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0090"/>
-    <s v="2025-09-15"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="848"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0091"/>
-    <s v="2025-09-16"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1024"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0092"/>
-    <s v="2025-09-16"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="840"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0093"/>
-    <s v="2025-09-16"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1139"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0094"/>
-    <s v="2025-09-16"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="701"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0095"/>
-    <s v="2025-09-16"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="913"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0096"/>
-    <s v="2025-09-16"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1189"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0097"/>
-    <s v="2025-09-17"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1363"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0098"/>
-    <s v="2025-09-17"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="873"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0099"/>
-    <s v="2025-09-17"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="513"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0100"/>
-    <s v="2025-09-17"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="621"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0101"/>
-    <s v="2025-09-17"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1407"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0102"/>
-    <s v="2025-09-17"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1246"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0103"/>
-    <s v="2025-09-18"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1208"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0104"/>
-    <s v="2025-09-18"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="878"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0105"/>
-    <s v="2025-09-18"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1399"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0106"/>
-    <s v="2025-09-18"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1193"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0107"/>
-    <s v="2025-09-18"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="640"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0108"/>
-    <s v="2025-09-18"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="628"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0109"/>
-    <s v="2025-09-19"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="760"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0110"/>
-    <s v="2025-09-19"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1288"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0111"/>
-    <s v="2025-09-19"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1466"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0112"/>
-    <s v="2025-09-19"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1446"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0113"/>
-    <s v="2025-09-19"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="538"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0114"/>
-    <s v="2025-09-19"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1451"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0115"/>
-    <s v="2025-09-20"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="794"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0116"/>
-    <s v="2025-09-20"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1165"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0117"/>
-    <s v="2025-09-20"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1133"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0118"/>
-    <s v="2025-09-20"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1113"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0119"/>
-    <s v="2025-09-20"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1372"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0120"/>
-    <s v="2025-09-20"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="618"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0121"/>
-    <s v="2025-09-21"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1198"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0122"/>
-    <s v="2025-09-21"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1139"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0123"/>
-    <s v="2025-09-21"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1494"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0124"/>
-    <s v="2025-09-21"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="780"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0125"/>
-    <s v="2025-09-21"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1463"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0126"/>
-    <s v="2025-09-21"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="677"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0127"/>
-    <s v="2025-09-22"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1196"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0128"/>
-    <s v="2025-09-22"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1076"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0129"/>
-    <s v="2025-09-22"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="735"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0130"/>
-    <s v="2025-09-22"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1049"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0131"/>
-    <s v="2025-09-22"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="515"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0132"/>
-    <s v="2025-09-22"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1430"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0133"/>
-    <s v="2025-09-23"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="631"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0134"/>
-    <s v="2025-09-23"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="703"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0135"/>
-    <s v="2025-09-23"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="696"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0136"/>
-    <s v="2025-09-23"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="649"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0137"/>
-    <s v="2025-09-23"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1087"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0138"/>
-    <s v="2025-09-23"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1373"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0139"/>
-    <s v="2025-09-24"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1176"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0140"/>
-    <s v="2025-09-24"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="509"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0141"/>
-    <s v="2025-09-24"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="652"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0142"/>
-    <s v="2025-09-24"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1129"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0143"/>
-    <s v="2025-09-24"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1005"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0144"/>
-    <s v="2025-09-24"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1477"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0145"/>
-    <s v="2025-09-25"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="628"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0146"/>
-    <s v="2025-09-25"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1319"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0147"/>
-    <s v="2025-09-25"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1009"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0148"/>
-    <s v="2025-09-25"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1177"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0149"/>
-    <s v="2025-09-25"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="988"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0150"/>
-    <s v="2025-09-25"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="969"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0151"/>
-    <s v="2025-09-26"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1288"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0152"/>
-    <s v="2025-09-26"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1134"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0153"/>
-    <s v="2025-09-26"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1027"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0154"/>
-    <s v="2025-09-26"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1415"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0155"/>
-    <s v="2025-09-26"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="969"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0156"/>
-    <s v="2025-09-26"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1330"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0157"/>
-    <s v="2025-09-27"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1141"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0158"/>
-    <s v="2025-09-27"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="624"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0159"/>
-    <s v="2025-09-27"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1490"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0160"/>
-    <s v="2025-09-27"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="707"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0161"/>
-    <s v="2025-09-27"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1198"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0162"/>
-    <s v="2025-09-27"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1081"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0163"/>
-    <s v="2025-09-28"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="677"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0164"/>
-    <s v="2025-09-28"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="817"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0165"/>
-    <s v="2025-09-28"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="550"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0166"/>
-    <s v="2025-09-28"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1309"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0167"/>
-    <s v="2025-09-28"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="685"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0168"/>
-    <s v="2025-09-28"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1200"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0169"/>
-    <s v="2025-09-29"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1178"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0170"/>
-    <s v="2025-09-29"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="1255"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0171"/>
-    <s v="2025-09-29"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="1079"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0172"/>
-    <s v="2025-09-29"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="551"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0173"/>
-    <s v="2025-09-29"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="759"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0174"/>
-    <s v="2025-09-29"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1227"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0175"/>
-    <s v="2025-09-30"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="964"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0176"/>
-    <s v="2025-09-30"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="757"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0177"/>
-    <s v="2025-09-30"/>
-    <x v="0"/>
-    <x v="2"/>
-    <n v="913"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0178"/>
-    <s v="2025-09-30"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1485"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0179"/>
-    <s v="2025-09-30"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="531"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <s v="PO-0180"/>
-    <s v="2025-09-30"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="1285"/>
-    <s v="KG"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <x v="3"/>
-    <m/>
-    <m/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8376931B-AA7E-4F06-9D71-D38A8838B705}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Cuenta de qty" fld="3" subtotal="count" baseField="2" baseItem="0"/>
-    <dataField name="Suma de qty" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5F7E753-F217-4F1A-9751-757E924312A9}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="6">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="2"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de qty" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6296,12 +1868,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tbl_sales_order_lines" displayName="Tbl_sales_order_lines" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tbl_sales_order_lines" displayName="Tbl_sales_order_lines" ref="A1:G61" totalsRowShown="0">
+  <autoFilter ref="A1:G61" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G61">
     <sortCondition ref="A1:A61"/>
   </sortState>
-  <tableColumns count="8">
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="so_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="line_no"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="item_id"/>
@@ -6309,9 +1881,6 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="uom"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="unit_price"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="currency"/>
-    <tableColumn id="8" xr3:uid="{BC011E9E-6269-42AA-806F-F4CFA3992E6D}" name="importe" dataDxfId="0">
-      <calculatedColumnFormula>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</calculatedColumnFormula>
-    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6328,7 +1897,7 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="qty"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="uom"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="batch"/>
-    <tableColumn id="8" xr3:uid="{A61C7632-5A63-4F91-B6F5-721E439D5759}" name="Columna1" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{A61C7632-5A63-4F91-B6F5-721E439D5759}" name="Columna1" dataDxfId="0">
       <calculatedColumnFormula>DAY(Tbl_plant_outputs[[#This Row],[output_date]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8730,97 +4299,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB0BE0EF-C9FF-4125-BCA7-CA4157375D60}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B3" t="s">
-        <v>577</v>
-      </c>
-      <c r="C3" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4">
-        <v>27</v>
-      </c>
-      <c r="C4" s="4">
-        <v>17266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="4">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4">
-        <v>9976</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="4">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4">
-        <v>10824</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="B8" s="4">
-        <v>60</v>
-      </c>
-      <c r="C8" s="4">
-        <v>38066</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -8842,11 +4325,8 @@
       <c r="G1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -8868,12 +4348,8 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="H2">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -8895,12 +4371,8 @@
       <c r="G3" t="s">
         <v>572</v>
       </c>
-      <c r="H3">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1197.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -8922,12 +4394,8 @@
       <c r="G4" t="s">
         <v>572</v>
       </c>
-      <c r="H4">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>483.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -8949,12 +4417,8 @@
       <c r="G5" t="s">
         <v>572</v>
       </c>
-      <c r="H5">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>477.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -8976,12 +4440,8 @@
       <c r="G6" t="s">
         <v>572</v>
       </c>
-      <c r="H6">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>484.90000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -9003,12 +4463,8 @@
       <c r="G7" t="s">
         <v>572</v>
       </c>
-      <c r="H7">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1176.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -9030,13 +4486,9 @@
       <c r="G8" t="s">
         <v>572</v>
       </c>
-      <c r="H8">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1271.4000000000001</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -9058,12 +4510,8 @@
       <c r="G9" t="s">
         <v>572</v>
       </c>
-      <c r="H9">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>673.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -9085,12 +4533,8 @@
       <c r="G10" t="s">
         <v>572</v>
       </c>
-      <c r="H10">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>816.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -9112,12 +4556,8 @@
       <c r="G11" t="s">
         <v>572</v>
       </c>
-      <c r="H11">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>682.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -9139,12 +4579,8 @@
       <c r="G12" t="s">
         <v>572</v>
       </c>
-      <c r="H12">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>972.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -9166,12 +4602,8 @@
       <c r="G13" t="s">
         <v>572</v>
       </c>
-      <c r="H13">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>864.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -9193,12 +4625,8 @@
       <c r="G14" t="s">
         <v>11</v>
       </c>
-      <c r="H14">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -9220,12 +4648,8 @@
       <c r="G15" t="s">
         <v>11</v>
       </c>
-      <c r="H15">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>920.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -9247,12 +4671,8 @@
       <c r="G16" t="s">
         <v>11</v>
       </c>
-      <c r="H16">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>685.19999999999993</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -9274,12 +4694,8 @@
       <c r="G17" t="s">
         <v>11</v>
       </c>
-      <c r="H17">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>498</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>65</v>
       </c>
@@ -9301,12 +4717,8 @@
       <c r="G18" t="s">
         <v>11</v>
       </c>
-      <c r="H18">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>474</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -9328,12 +4740,8 @@
       <c r="G19" t="s">
         <v>11</v>
       </c>
-      <c r="H19">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -9355,12 +4763,8 @@
       <c r="G20" t="s">
         <v>11</v>
       </c>
-      <c r="H20">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>645.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -9382,12 +4786,8 @@
       <c r="G21" t="s">
         <v>11</v>
       </c>
-      <c r="H21">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>630</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -9409,12 +4809,8 @@
       <c r="G22" t="s">
         <v>11</v>
       </c>
-      <c r="H22">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>991.19999999999993</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -9436,12 +4832,8 @@
       <c r="G23" t="s">
         <v>11</v>
       </c>
-      <c r="H23">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>223.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -9463,12 +4855,8 @@
       <c r="G24" t="s">
         <v>11</v>
       </c>
-      <c r="H24">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -9490,12 +4878,8 @@
       <c r="G25" t="s">
         <v>11</v>
       </c>
-      <c r="H25">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -9517,12 +4901,8 @@
       <c r="G26" t="s">
         <v>11</v>
       </c>
-      <c r="H26">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -9544,12 +4924,8 @@
       <c r="G27" t="s">
         <v>11</v>
       </c>
-      <c r="H27">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>844.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>75</v>
       </c>
@@ -9571,12 +4947,8 @@
       <c r="G28" t="s">
         <v>11</v>
       </c>
-      <c r="H28">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>153.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -9598,12 +4970,8 @@
       <c r="G29" t="s">
         <v>572</v>
       </c>
-      <c r="H29">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>300.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -9625,12 +4993,8 @@
       <c r="G30" t="s">
         <v>572</v>
       </c>
-      <c r="H30">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>551.20000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -9652,12 +5016,8 @@
       <c r="G31" t="s">
         <v>572</v>
       </c>
-      <c r="H31">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>183.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -9679,12 +5039,8 @@
       <c r="G32" t="s">
         <v>11</v>
       </c>
-      <c r="H32">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1195.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -9706,12 +5062,8 @@
       <c r="G33" t="s">
         <v>11</v>
       </c>
-      <c r="H33">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1105.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -9733,12 +5085,8 @@
       <c r="G34" t="s">
         <v>11</v>
       </c>
-      <c r="H34">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>633.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -9760,12 +5108,8 @@
       <c r="G35" t="s">
         <v>11</v>
       </c>
-      <c r="H35">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1113.5999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -9787,12 +5131,8 @@
       <c r="G36" t="s">
         <v>11</v>
       </c>
-      <c r="H36">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -9814,12 +5154,8 @@
       <c r="G37" t="s">
         <v>11</v>
       </c>
-      <c r="H37">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>966</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -9841,12 +5177,8 @@
       <c r="G38" t="s">
         <v>11</v>
       </c>
-      <c r="H38">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>190.79999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -9868,12 +5200,8 @@
       <c r="G39" t="s">
         <v>11</v>
       </c>
-      <c r="H39">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>832.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -9895,12 +5223,8 @@
       <c r="G40" t="s">
         <v>11</v>
       </c>
-      <c r="H40">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>362.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -9922,12 +5246,8 @@
       <c r="G41" t="s">
         <v>11</v>
       </c>
-      <c r="H41">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>861.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -9949,12 +5269,8 @@
       <c r="G42" t="s">
         <v>11</v>
       </c>
-      <c r="H42">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>694.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>90</v>
       </c>
@@ -9976,12 +5292,8 @@
       <c r="G43" t="s">
         <v>11</v>
       </c>
-      <c r="H43">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>423.59999999999997</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -10003,12 +5315,8 @@
       <c r="G44" t="s">
         <v>11</v>
       </c>
-      <c r="H44">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>944.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -10030,12 +5338,8 @@
       <c r="G45" t="s">
         <v>11</v>
       </c>
-      <c r="H45">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1022.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -10057,12 +5361,8 @@
       <c r="G46" t="s">
         <v>11</v>
       </c>
-      <c r="H46">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>394.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -10084,12 +5384,8 @@
       <c r="G47" t="s">
         <v>11</v>
       </c>
-      <c r="H47">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>428.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -10111,12 +5407,8 @@
       <c r="G48" t="s">
         <v>572</v>
       </c>
-      <c r="H48">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>648.70000000000005</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -10138,12 +5430,8 @@
       <c r="G49" t="s">
         <v>572</v>
       </c>
-      <c r="H49">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>789.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -10165,12 +5453,8 @@
       <c r="G50" t="s">
         <v>572</v>
       </c>
-      <c r="H50">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1179.1000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -10192,12 +5476,8 @@
       <c r="G51" t="s">
         <v>11</v>
       </c>
-      <c r="H51">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1160.3999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>99</v>
       </c>
@@ -10219,12 +5499,8 @@
       <c r="G52" t="s">
         <v>11</v>
       </c>
-      <c r="H52">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>558</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>100</v>
       </c>
@@ -10246,12 +5522,8 @@
       <c r="G53" t="s">
         <v>11</v>
       </c>
-      <c r="H53">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>477.59999999999997</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>101</v>
       </c>
@@ -10273,12 +5545,8 @@
       <c r="G54" t="s">
         <v>11</v>
       </c>
-      <c r="H54">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>710.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>102</v>
       </c>
@@ -10300,12 +5568,8 @@
       <c r="G55" t="s">
         <v>11</v>
       </c>
-      <c r="H55">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1040.3999999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>103</v>
       </c>
@@ -10327,12 +5591,8 @@
       <c r="G56" t="s">
         <v>11</v>
       </c>
-      <c r="H56">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>152.4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -10354,12 +5614,8 @@
       <c r="G57" t="s">
         <v>11</v>
       </c>
-      <c r="H57">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1107.5999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>105</v>
       </c>
@@ -10381,12 +5637,8 @@
       <c r="G58" t="s">
         <v>572</v>
       </c>
-      <c r="H58">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>699.6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>106</v>
       </c>
@@ -10408,12 +5660,8 @@
       <c r="G59" t="s">
         <v>572</v>
       </c>
-      <c r="H59">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>1065.5999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>107</v>
       </c>
@@ -10435,12 +5683,8 @@
       <c r="G60" t="s">
         <v>572</v>
       </c>
-      <c r="H60">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>960</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>108</v>
       </c>
@@ -10461,10 +5705,6 @@
       </c>
       <c r="G61" t="s">
         <v>11</v>
-      </c>
-      <c r="H61">
-        <f>Tbl_sales_order_lines[[#This Row],[qty]]*Tbl_sales_order_lines[[#This Row],[unit_price]]</f>
-        <v>544.79999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -10475,114 +5715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EFB1EFC-9E09-49FA-9385-B0CEA0292B41}">
-  <dimension ref="A3:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B3" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4">
-        <v>91820</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4">
-        <v>31288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="4">
-        <v>30255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="4">
-        <v>30277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B8" s="4">
-        <v>91706</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="4">
-        <v>30094</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="4">
-        <v>29100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="4">
-        <v>32512</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="B14" s="4">
-        <v>183526</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
